--- a/ZAKAT FITRAH 2026.xlsx
+++ b/ZAKAT FITRAH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP Laptop\OneDrive\Desktop\IRMADA\FORM_ZAKAT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A9E5B05-0678-4CA6-AE03-79C238F693C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D4D5E00-283E-41F0-8696-24332D540782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1620" yWindow="2715" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -166,7 +166,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -308,11 +308,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -330,15 +354,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -346,47 +363,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -411,6 +391,18 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -420,11 +412,480 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="13">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD0E0E3"/>
+          <bgColor rgb="FFD0E0E3"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -435,6 +896,25 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7202A943-04D6-4FD8-80B8-4B3D0FF1D171}" name="Table1" displayName="Table1" ref="A5:J206" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" tableBorderDxfId="12">
+  <autoFilter ref="A5:J206" xr:uid="{7202A943-04D6-4FD8-80B8-4B3D0FF1D171}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{E8A2D6F3-0316-432F-9EFF-53BA71D6A9A7}" name="No" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{D7219358-5294-4FDC-B4B5-55120E90E5BE}" name="Tanggal" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{839AD55F-9D70-4ABD-B6E9-B5DCA5429422}" name="Jam" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{ADF7AA8A-918B-4BE7-BE80-E3416E7F7483}" name="Nama" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{CDDBF9DF-57CF-4C54-81DF-B2969CE5BBF7}" name="Alamat" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{0CA1ECD5-6F2E-475A-A061-926D2690661A}" name="RT" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{45F2CCED-0606-41F1-A337-B147DA3BE3BC}" name="RW" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{B7BD0624-8337-4220-9503-7F3E929A4D89}" name="KATEGORI" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{D36BF81F-1311-41A5-8310-3A93234D1D07}" name="JUMLAH JIWA" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{5F1228E6-2D4E-43B4-9C01-41B9347E31B3}" name="JUMLAH BERAS" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -635,7 +1115,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Q1003"/>
@@ -643,7 +1123,7 @@
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" customWidth="1"/>
     <col min="9" max="9" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -655,90 +1135,90 @@
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
     </row>
     <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
     </row>
     <row r="4" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:17" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:17" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="G5" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="H5" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="17" t="s">
+      <c r="J5" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="7"/>
-      <c r="M5" s="26"/>
-      <c r="N5" s="27"/>
-    </row>
-    <row r="6" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="9"/>
+      <c r="K5" s="36"/>
+      <c r="M5" s="30"/>
+      <c r="N5" s="31"/>
+    </row>
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="34"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="46"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="37"/>
+      <c r="L6" s="7"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
     </row>
     <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="3"/>
+      <c r="A7" s="35"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -748,11 +1228,11 @@
       <c r="H7" s="3"/>
       <c r="I7" s="4"/>
       <c r="J7" s="5"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="11"/>
+      <c r="K7" s="38"/>
+      <c r="L7" s="8"/>
     </row>
     <row r="8" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="3"/>
+      <c r="A8" s="35"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
@@ -762,11 +1242,11 @@
       <c r="H8" s="3"/>
       <c r="I8" s="4"/>
       <c r="J8" s="5"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="11"/>
+      <c r="K8" s="38"/>
+      <c r="L8" s="8"/>
     </row>
     <row r="9" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="3"/>
+      <c r="A9" s="35"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
@@ -776,18 +1256,18 @@
       <c r="H9" s="3"/>
       <c r="I9" s="4"/>
       <c r="J9" s="5"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="28" t="s">
+      <c r="K9" s="38"/>
+      <c r="L9" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="29"/>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="30"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="14"/>
     </row>
     <row r="10" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="3"/>
+      <c r="A10" s="35"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
@@ -797,16 +1277,16 @@
       <c r="H10" s="3"/>
       <c r="I10" s="4"/>
       <c r="J10" s="5"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="32"/>
-      <c r="N10" s="32"/>
-      <c r="O10" s="32"/>
-      <c r="P10" s="32"/>
-      <c r="Q10" s="33"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="16"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="17"/>
     </row>
     <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="3"/>
+      <c r="A11" s="35"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
@@ -816,21 +1296,21 @@
       <c r="H11" s="3"/>
       <c r="I11" s="4"/>
       <c r="J11" s="5"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="34" t="s">
+      <c r="K11" s="38"/>
+      <c r="L11" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M11" s="20">
+      <c r="M11" s="21">
         <f>SUMIF(H7:H206, "perorangan", I7:I206)</f>
         <v>0</v>
       </c>
-      <c r="N11" s="21"/>
-      <c r="O11" s="21"/>
-      <c r="P11" s="21"/>
-      <c r="Q11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="23"/>
     </row>
     <row r="12" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="3"/>
+      <c r="A12" s="35"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
@@ -840,16 +1320,16 @@
       <c r="H12" s="3"/>
       <c r="I12" s="4"/>
       <c r="J12" s="5"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="35"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="24"/>
-      <c r="O12" s="24"/>
-      <c r="P12" s="24"/>
-      <c r="Q12" s="25"/>
+      <c r="K12" s="38"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="27"/>
+      <c r="N12" s="28"/>
+      <c r="O12" s="28"/>
+      <c r="P12" s="28"/>
+      <c r="Q12" s="29"/>
     </row>
     <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="3"/>
+      <c r="A13" s="35"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -859,21 +1339,21 @@
       <c r="H13" s="3"/>
       <c r="I13" s="4"/>
       <c r="J13" s="5"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="19" t="s">
+      <c r="K13" s="38"/>
+      <c r="L13" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="M13" s="19">
+      <c r="M13" s="20">
         <f>SUMIF(H7:H206, "instansi", I7:I206)</f>
         <v>0</v>
       </c>
-      <c r="N13" s="19"/>
-      <c r="O13" s="19"/>
-      <c r="P13" s="19"/>
-      <c r="Q13" s="19"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20"/>
     </row>
     <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="3"/>
+      <c r="A14" s="35"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -883,16 +1363,16 @@
       <c r="H14" s="3"/>
       <c r="I14" s="4"/>
       <c r="J14" s="5"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="19"/>
-      <c r="N14" s="19"/>
-      <c r="O14" s="19"/>
-      <c r="P14" s="19"/>
-      <c r="Q14" s="19"/>
+      <c r="K14" s="38"/>
+      <c r="L14" s="20"/>
+      <c r="M14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20"/>
     </row>
     <row r="15" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="3"/>
+      <c r="A15" s="35"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -902,21 +1382,21 @@
       <c r="H15" s="3"/>
       <c r="I15" s="4"/>
       <c r="J15" s="5"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="19" t="s">
+      <c r="K15" s="38"/>
+      <c r="L15" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="M15" s="19">
+      <c r="M15" s="20">
         <f>SUM(L7:L206)</f>
         <v>0</v>
       </c>
-      <c r="N15" s="19"/>
-      <c r="O15" s="19"/>
-      <c r="P15" s="19"/>
-      <c r="Q15" s="19"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20"/>
     </row>
     <row r="16" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="3"/>
+      <c r="A16" s="35"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -926,16 +1406,16 @@
       <c r="H16" s="3"/>
       <c r="I16" s="4"/>
       <c r="J16" s="5"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="19"/>
-      <c r="Q16" s="19"/>
+      <c r="K16" s="38"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20"/>
     </row>
     <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="3"/>
+      <c r="A17" s="35"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -945,16 +1425,16 @@
       <c r="H17" s="3"/>
       <c r="I17" s="4"/>
       <c r="J17" s="5"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
-      <c r="N17" s="12"/>
-      <c r="O17" s="12"/>
-      <c r="P17" s="12"/>
-      <c r="Q17" s="12"/>
+      <c r="K17" s="38"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="9"/>
     </row>
     <row r="18" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="3"/>
+      <c r="A18" s="35"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -964,16 +1444,16 @@
       <c r="H18" s="3"/>
       <c r="I18" s="4"/>
       <c r="J18" s="5"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
-      <c r="N18" s="12"/>
-      <c r="O18" s="12"/>
-      <c r="P18" s="12"/>
-      <c r="Q18" s="12"/>
+      <c r="K18" s="38"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="9"/>
     </row>
     <row r="19" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="3"/>
+      <c r="A19" s="35"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -983,16 +1463,16 @@
       <c r="H19" s="3"/>
       <c r="I19" s="4"/>
       <c r="J19" s="5"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="12"/>
-      <c r="M19" s="12"/>
-      <c r="N19" s="12"/>
-      <c r="O19" s="12"/>
-      <c r="P19" s="12"/>
-      <c r="Q19" s="12"/>
+      <c r="K19" s="38"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="9"/>
+      <c r="Q19" s="9"/>
     </row>
     <row r="20" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="3"/>
+      <c r="A20" s="35"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -1002,18 +1482,18 @@
       <c r="H20" s="3"/>
       <c r="I20" s="4"/>
       <c r="J20" s="5"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="28" t="s">
+      <c r="K20" s="38"/>
+      <c r="L20" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="M20" s="29"/>
-      <c r="N20" s="29"/>
-      <c r="O20" s="29"/>
-      <c r="P20" s="29"/>
-      <c r="Q20" s="30"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13"/>
+      <c r="P20" s="13"/>
+      <c r="Q20" s="14"/>
     </row>
     <row r="21" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="3"/>
+      <c r="A21" s="35"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -1023,16 +1503,16 @@
       <c r="H21" s="3"/>
       <c r="I21" s="4"/>
       <c r="J21" s="5"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="31"/>
-      <c r="M21" s="32"/>
-      <c r="N21" s="32"/>
-      <c r="O21" s="32"/>
-      <c r="P21" s="32"/>
-      <c r="Q21" s="33"/>
+      <c r="K21" s="38"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="16"/>
+      <c r="N21" s="16"/>
+      <c r="O21" s="16"/>
+      <c r="P21" s="16"/>
+      <c r="Q21" s="17"/>
     </row>
     <row r="22" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="3"/>
+      <c r="A22" s="35"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -1042,21 +1522,21 @@
       <c r="H22" s="3"/>
       <c r="I22" s="4"/>
       <c r="J22" s="5"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="34" t="s">
+      <c r="K22" s="38"/>
+      <c r="L22" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M22" s="20">
+      <c r="M22" s="21">
         <f>SUMIF(H7:H222, "perorangan", J7:J222)</f>
         <v>0</v>
       </c>
-      <c r="N22" s="21"/>
-      <c r="O22" s="21"/>
-      <c r="P22" s="21"/>
-      <c r="Q22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="23"/>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="3"/>
+      <c r="A23" s="35"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -1066,16 +1546,16 @@
       <c r="H23" s="3"/>
       <c r="I23" s="4"/>
       <c r="J23" s="5"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="35"/>
-      <c r="M23" s="36"/>
-      <c r="N23" s="37"/>
-      <c r="O23" s="37"/>
-      <c r="P23" s="37"/>
-      <c r="Q23" s="38"/>
+      <c r="K23" s="38"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="24"/>
+      <c r="N23" s="25"/>
+      <c r="O23" s="25"/>
+      <c r="P23" s="25"/>
+      <c r="Q23" s="26"/>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="3"/>
+      <c r="A24" s="35"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
@@ -1085,21 +1565,21 @@
       <c r="H24" s="3"/>
       <c r="I24" s="4"/>
       <c r="J24" s="5"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="19" t="s">
+      <c r="K24" s="38"/>
+      <c r="L24" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="M24" s="19">
+      <c r="M24" s="20">
         <f>SUMIF(H7:H222, "instansi", J7:J222)</f>
         <v>0</v>
       </c>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20"/>
     </row>
     <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="3"/>
+      <c r="A25" s="35"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -1109,16 +1589,16 @@
       <c r="H25" s="3"/>
       <c r="I25" s="4"/>
       <c r="J25" s="5"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="34"/>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19"/>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
+      <c r="K25" s="38"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20"/>
     </row>
     <row r="26" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="3"/>
+      <c r="A26" s="35"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
@@ -1128,21 +1608,21 @@
       <c r="H26" s="3"/>
       <c r="I26" s="4"/>
       <c r="J26" s="5"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="35" t="s">
+      <c r="K26" s="38"/>
+      <c r="L26" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="M26" s="19">
+      <c r="M26" s="20">
         <f>SUM(J7:J206)</f>
         <v>0</v>
       </c>
-      <c r="N26" s="19"/>
-      <c r="O26" s="19"/>
-      <c r="P26" s="19"/>
-      <c r="Q26" s="19"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="20"/>
     </row>
     <row r="27" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="3"/>
+      <c r="A27" s="35"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -1152,16 +1632,16 @@
       <c r="H27" s="3"/>
       <c r="I27" s="4"/>
       <c r="J27" s="5"/>
-      <c r="K27" s="10"/>
-      <c r="L27" s="19"/>
-      <c r="M27" s="19"/>
-      <c r="N27" s="19"/>
-      <c r="O27" s="19"/>
-      <c r="P27" s="19"/>
-      <c r="Q27" s="19"/>
+      <c r="K27" s="38"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="20"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="20"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="20"/>
     </row>
     <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="3"/>
+      <c r="A28" s="35"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
@@ -1171,10 +1651,10 @@
       <c r="H28" s="3"/>
       <c r="I28" s="4"/>
       <c r="J28" s="5"/>
-      <c r="K28" s="10"/>
+      <c r="K28" s="38"/>
     </row>
     <row r="29" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="3"/>
+      <c r="A29" s="35"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
@@ -1184,10 +1664,10 @@
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="6"/>
-      <c r="K29" s="10"/>
+      <c r="K29" s="38"/>
     </row>
     <row r="30" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="3"/>
+      <c r="A30" s="35"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
@@ -1197,16 +1677,16 @@
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="6"/>
-      <c r="K30" s="10"/>
-      <c r="L30" s="12"/>
-      <c r="M30" s="12"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="12"/>
-      <c r="P30" s="12"/>
-      <c r="Q30" s="12"/>
+      <c r="K30" s="38"/>
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
+      <c r="N30" s="9"/>
+      <c r="O30" s="9"/>
+      <c r="P30" s="9"/>
+      <c r="Q30" s="9"/>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="3"/>
+      <c r="A31" s="35"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
@@ -1216,16 +1696,16 @@
       <c r="H31" s="3"/>
       <c r="I31" s="4"/>
       <c r="J31" s="5"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="12"/>
-      <c r="N31" s="12"/>
-      <c r="O31" s="12"/>
-      <c r="P31" s="12"/>
-      <c r="Q31" s="12"/>
+      <c r="K31" s="38"/>
+      <c r="L31" s="9"/>
+      <c r="M31" s="9"/>
+      <c r="N31" s="9"/>
+      <c r="O31" s="9"/>
+      <c r="P31" s="9"/>
+      <c r="Q31" s="9"/>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="3"/>
+      <c r="A32" s="35"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
@@ -1235,10 +1715,10 @@
       <c r="H32" s="3"/>
       <c r="I32" s="4"/>
       <c r="J32" s="5"/>
-      <c r="K32" s="10"/>
+      <c r="K32" s="38"/>
     </row>
     <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="3"/>
+      <c r="A33" s="35"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
@@ -1248,10 +1728,10 @@
       <c r="H33" s="3"/>
       <c r="I33" s="4"/>
       <c r="J33" s="5"/>
-      <c r="K33" s="10"/>
+      <c r="K33" s="38"/>
     </row>
     <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="3"/>
+      <c r="A34" s="35"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
@@ -1261,10 +1741,10 @@
       <c r="H34" s="3"/>
       <c r="I34" s="4"/>
       <c r="J34" s="5"/>
-      <c r="K34" s="10"/>
+      <c r="K34" s="38"/>
     </row>
     <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="3"/>
+      <c r="A35" s="35"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
@@ -1274,10 +1754,10 @@
       <c r="H35" s="3"/>
       <c r="I35" s="4"/>
       <c r="J35" s="5"/>
-      <c r="K35" s="10"/>
+      <c r="K35" s="38"/>
     </row>
     <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="3"/>
+      <c r="A36" s="35"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
@@ -1287,10 +1767,10 @@
       <c r="H36" s="3"/>
       <c r="I36" s="4"/>
       <c r="J36" s="5"/>
-      <c r="K36" s="10"/>
+      <c r="K36" s="38"/>
     </row>
     <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="3"/>
+      <c r="A37" s="35"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
@@ -1300,10 +1780,10 @@
       <c r="H37" s="3"/>
       <c r="I37" s="4"/>
       <c r="J37" s="5"/>
-      <c r="K37" s="10"/>
+      <c r="K37" s="38"/>
     </row>
     <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="3"/>
+      <c r="A38" s="35"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
@@ -1313,10 +1793,10 @@
       <c r="H38" s="3"/>
       <c r="I38" s="4"/>
       <c r="J38" s="5"/>
-      <c r="K38" s="10"/>
+      <c r="K38" s="38"/>
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="3"/>
+      <c r="A39" s="35"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
@@ -1326,11 +1806,11 @@
       <c r="H39" s="3"/>
       <c r="I39" s="4"/>
       <c r="J39" s="5"/>
-      <c r="K39" s="10"/>
-      <c r="L39" s="11"/>
+      <c r="K39" s="38"/>
+      <c r="L39" s="8"/>
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="3"/>
+      <c r="A40" s="35"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
@@ -1340,11 +1820,11 @@
       <c r="H40" s="3"/>
       <c r="I40" s="4"/>
       <c r="J40" s="5"/>
-      <c r="K40" s="10"/>
-      <c r="L40" s="11"/>
+      <c r="K40" s="38"/>
+      <c r="L40" s="8"/>
     </row>
     <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="3"/>
+      <c r="A41" s="35"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
@@ -1354,11 +1834,11 @@
       <c r="H41" s="3"/>
       <c r="I41" s="4"/>
       <c r="J41" s="5"/>
-      <c r="K41" s="10"/>
-      <c r="L41" s="11"/>
+      <c r="K41" s="38"/>
+      <c r="L41" s="8"/>
     </row>
     <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="3"/>
+      <c r="A42" s="35"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
@@ -1368,11 +1848,11 @@
       <c r="H42" s="3"/>
       <c r="I42" s="4"/>
       <c r="J42" s="5"/>
-      <c r="K42" s="10"/>
-      <c r="L42" s="11"/>
+      <c r="K42" s="38"/>
+      <c r="L42" s="8"/>
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="3"/>
+      <c r="A43" s="35"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
@@ -1382,11 +1862,11 @@
       <c r="H43" s="3"/>
       <c r="I43" s="4"/>
       <c r="J43" s="5"/>
-      <c r="K43" s="10"/>
-      <c r="L43" s="11"/>
+      <c r="K43" s="38"/>
+      <c r="L43" s="8"/>
     </row>
     <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="3"/>
+      <c r="A44" s="35"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
@@ -1396,11 +1876,11 @@
       <c r="H44" s="3"/>
       <c r="I44" s="4"/>
       <c r="J44" s="5"/>
-      <c r="K44" s="10"/>
-      <c r="L44" s="11"/>
+      <c r="K44" s="38"/>
+      <c r="L44" s="8"/>
     </row>
     <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="3"/>
+      <c r="A45" s="35"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
@@ -1410,11 +1890,11 @@
       <c r="H45" s="3"/>
       <c r="I45" s="4"/>
       <c r="J45" s="5"/>
-      <c r="K45" s="10"/>
-      <c r="L45" s="11"/>
+      <c r="K45" s="38"/>
+      <c r="L45" s="8"/>
     </row>
     <row r="46" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="3"/>
+      <c r="A46" s="35"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
@@ -1424,11 +1904,11 @@
       <c r="H46" s="3"/>
       <c r="I46" s="4"/>
       <c r="J46" s="5"/>
-      <c r="K46" s="10"/>
-      <c r="L46" s="11"/>
+      <c r="K46" s="38"/>
+      <c r="L46" s="8"/>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="3"/>
+      <c r="A47" s="35"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
@@ -1438,11 +1918,11 @@
       <c r="H47" s="3"/>
       <c r="I47" s="4"/>
       <c r="J47" s="5"/>
-      <c r="K47" s="10"/>
-      <c r="L47" s="11"/>
+      <c r="K47" s="38"/>
+      <c r="L47" s="8"/>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="3"/>
+      <c r="A48" s="35"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
@@ -1452,11 +1932,11 @@
       <c r="H48" s="3"/>
       <c r="I48" s="4"/>
       <c r="J48" s="5"/>
-      <c r="K48" s="10"/>
-      <c r="L48" s="11"/>
+      <c r="K48" s="38"/>
+      <c r="L48" s="8"/>
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="3"/>
+      <c r="A49" s="35"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
@@ -1466,11 +1946,11 @@
       <c r="H49" s="3"/>
       <c r="I49" s="4"/>
       <c r="J49" s="5"/>
-      <c r="K49" s="10"/>
-      <c r="L49" s="11"/>
+      <c r="K49" s="38"/>
+      <c r="L49" s="8"/>
     </row>
     <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="3"/>
+      <c r="A50" s="35"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
@@ -1480,11 +1960,11 @@
       <c r="H50" s="3"/>
       <c r="I50" s="4"/>
       <c r="J50" s="5"/>
-      <c r="K50" s="10"/>
-      <c r="L50" s="11"/>
+      <c r="K50" s="38"/>
+      <c r="L50" s="8"/>
     </row>
     <row r="51" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="3"/>
+      <c r="A51" s="35"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
@@ -1494,11 +1974,11 @@
       <c r="H51" s="3"/>
       <c r="I51" s="4"/>
       <c r="J51" s="5"/>
-      <c r="K51" s="10"/>
-      <c r="L51" s="11"/>
+      <c r="K51" s="38"/>
+      <c r="L51" s="8"/>
     </row>
     <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="3"/>
+      <c r="A52" s="35"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
@@ -1508,11 +1988,11 @@
       <c r="H52" s="3"/>
       <c r="I52" s="4"/>
       <c r="J52" s="5"/>
-      <c r="K52" s="10"/>
-      <c r="L52" s="11"/>
+      <c r="K52" s="38"/>
+      <c r="L52" s="8"/>
     </row>
     <row r="53" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="3"/>
+      <c r="A53" s="35"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
@@ -1522,11 +2002,11 @@
       <c r="H53" s="3"/>
       <c r="I53" s="4"/>
       <c r="J53" s="5"/>
-      <c r="K53" s="10"/>
-      <c r="L53" s="11"/>
+      <c r="K53" s="38"/>
+      <c r="L53" s="8"/>
     </row>
     <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="3"/>
+      <c r="A54" s="35"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
@@ -1536,11 +2016,11 @@
       <c r="H54" s="3"/>
       <c r="I54" s="4"/>
       <c r="J54" s="5"/>
-      <c r="K54" s="10"/>
-      <c r="L54" s="11"/>
+      <c r="K54" s="38"/>
+      <c r="L54" s="8"/>
     </row>
     <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="3"/>
+      <c r="A55" s="35"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
@@ -1550,11 +2030,11 @@
       <c r="H55" s="3"/>
       <c r="I55" s="4"/>
       <c r="J55" s="5"/>
-      <c r="K55" s="10"/>
-      <c r="L55" s="11"/>
+      <c r="K55" s="38"/>
+      <c r="L55" s="8"/>
     </row>
     <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="3"/>
+      <c r="A56" s="35"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
@@ -1564,11 +2044,11 @@
       <c r="H56" s="3"/>
       <c r="I56" s="4"/>
       <c r="J56" s="5"/>
-      <c r="K56" s="10"/>
-      <c r="L56" s="11"/>
+      <c r="K56" s="38"/>
+      <c r="L56" s="8"/>
     </row>
     <row r="57" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="3"/>
+      <c r="A57" s="35"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
@@ -1578,11 +2058,11 @@
       <c r="H57" s="3"/>
       <c r="I57" s="4"/>
       <c r="J57" s="5"/>
-      <c r="K57" s="10"/>
-      <c r="L57" s="11"/>
+      <c r="K57" s="38"/>
+      <c r="L57" s="8"/>
     </row>
     <row r="58" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="3"/>
+      <c r="A58" s="35"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
@@ -1592,11 +2072,11 @@
       <c r="H58" s="3"/>
       <c r="I58" s="4"/>
       <c r="J58" s="5"/>
-      <c r="K58" s="10"/>
-      <c r="L58" s="11"/>
+      <c r="K58" s="38"/>
+      <c r="L58" s="8"/>
     </row>
     <row r="59" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="3"/>
+      <c r="A59" s="35"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
@@ -1606,11 +2086,11 @@
       <c r="H59" s="3"/>
       <c r="I59" s="4"/>
       <c r="J59" s="5"/>
-      <c r="K59" s="10"/>
-      <c r="L59" s="11"/>
+      <c r="K59" s="38"/>
+      <c r="L59" s="8"/>
     </row>
     <row r="60" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="3"/>
+      <c r="A60" s="35"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
@@ -1620,11 +2100,11 @@
       <c r="H60" s="3"/>
       <c r="I60" s="4"/>
       <c r="J60" s="5"/>
-      <c r="K60" s="10"/>
-      <c r="L60" s="11"/>
+      <c r="K60" s="38"/>
+      <c r="L60" s="8"/>
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="3"/>
+      <c r="A61" s="35"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
@@ -1634,11 +2114,11 @@
       <c r="H61" s="3"/>
       <c r="I61" s="4"/>
       <c r="J61" s="5"/>
-      <c r="K61" s="10"/>
-      <c r="L61" s="11"/>
+      <c r="K61" s="38"/>
+      <c r="L61" s="8"/>
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="3"/>
+      <c r="A62" s="35"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
@@ -1648,11 +2128,11 @@
       <c r="H62" s="3"/>
       <c r="I62" s="4"/>
       <c r="J62" s="5"/>
-      <c r="K62" s="10"/>
-      <c r="L62" s="11"/>
+      <c r="K62" s="38"/>
+      <c r="L62" s="8"/>
     </row>
     <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="3"/>
+      <c r="A63" s="35"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
@@ -1662,11 +2142,11 @@
       <c r="H63" s="3"/>
       <c r="I63" s="4"/>
       <c r="J63" s="5"/>
-      <c r="K63" s="10"/>
-      <c r="L63" s="11"/>
+      <c r="K63" s="38"/>
+      <c r="L63" s="8"/>
     </row>
     <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="3"/>
+      <c r="A64" s="35"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
@@ -1676,11 +2156,11 @@
       <c r="H64" s="3"/>
       <c r="I64" s="4"/>
       <c r="J64" s="5"/>
-      <c r="K64" s="10"/>
-      <c r="L64" s="11"/>
+      <c r="K64" s="38"/>
+      <c r="L64" s="8"/>
     </row>
     <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="3"/>
+      <c r="A65" s="35"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
@@ -1690,11 +2170,11 @@
       <c r="H65" s="3"/>
       <c r="I65" s="4"/>
       <c r="J65" s="5"/>
-      <c r="K65" s="10"/>
-      <c r="L65" s="11"/>
+      <c r="K65" s="38"/>
+      <c r="L65" s="8"/>
     </row>
     <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="3"/>
+      <c r="A66" s="35"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
@@ -1704,11 +2184,11 @@
       <c r="H66" s="3"/>
       <c r="I66" s="4"/>
       <c r="J66" s="5"/>
-      <c r="K66" s="10"/>
-      <c r="L66" s="11"/>
+      <c r="K66" s="38"/>
+      <c r="L66" s="8"/>
     </row>
     <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="3"/>
+      <c r="A67" s="35"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
@@ -1718,11 +2198,11 @@
       <c r="H67" s="3"/>
       <c r="I67" s="4"/>
       <c r="J67" s="5"/>
-      <c r="K67" s="10"/>
-      <c r="L67" s="11"/>
+      <c r="K67" s="38"/>
+      <c r="L67" s="8"/>
     </row>
     <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="3"/>
+      <c r="A68" s="35"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
@@ -1732,11 +2212,11 @@
       <c r="H68" s="3"/>
       <c r="I68" s="4"/>
       <c r="J68" s="5"/>
-      <c r="K68" s="10"/>
-      <c r="L68" s="11"/>
+      <c r="K68" s="38"/>
+      <c r="L68" s="8"/>
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="3"/>
+      <c r="A69" s="35"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
@@ -1746,11 +2226,11 @@
       <c r="H69" s="3"/>
       <c r="I69" s="4"/>
       <c r="J69" s="5"/>
-      <c r="K69" s="10"/>
-      <c r="L69" s="11"/>
+      <c r="K69" s="38"/>
+      <c r="L69" s="8"/>
     </row>
     <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="3"/>
+      <c r="A70" s="35"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
@@ -1760,11 +2240,11 @@
       <c r="H70" s="3"/>
       <c r="I70" s="4"/>
       <c r="J70" s="5"/>
-      <c r="K70" s="10"/>
-      <c r="L70" s="11"/>
+      <c r="K70" s="38"/>
+      <c r="L70" s="8"/>
     </row>
     <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="3"/>
+      <c r="A71" s="35"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
@@ -1774,11 +2254,11 @@
       <c r="H71" s="3"/>
       <c r="I71" s="4"/>
       <c r="J71" s="5"/>
-      <c r="K71" s="10"/>
-      <c r="L71" s="11"/>
+      <c r="K71" s="38"/>
+      <c r="L71" s="8"/>
     </row>
     <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="3"/>
+      <c r="A72" s="35"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
@@ -1788,11 +2268,11 @@
       <c r="H72" s="3"/>
       <c r="I72" s="4"/>
       <c r="J72" s="5"/>
-      <c r="K72" s="10"/>
-      <c r="L72" s="11"/>
+      <c r="K72" s="38"/>
+      <c r="L72" s="8"/>
     </row>
     <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="3"/>
+      <c r="A73" s="35"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
@@ -1802,11 +2282,11 @@
       <c r="H73" s="3"/>
       <c r="I73" s="4"/>
       <c r="J73" s="5"/>
-      <c r="K73" s="10"/>
-      <c r="L73" s="11"/>
+      <c r="K73" s="38"/>
+      <c r="L73" s="8"/>
     </row>
     <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="3"/>
+      <c r="A74" s="35"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
@@ -1816,11 +2296,11 @@
       <c r="H74" s="3"/>
       <c r="I74" s="4"/>
       <c r="J74" s="5"/>
-      <c r="K74" s="10"/>
-      <c r="L74" s="11"/>
+      <c r="K74" s="38"/>
+      <c r="L74" s="8"/>
     </row>
     <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="3"/>
+      <c r="A75" s="35"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
@@ -1830,11 +2310,11 @@
       <c r="H75" s="3"/>
       <c r="I75" s="4"/>
       <c r="J75" s="5"/>
-      <c r="K75" s="10"/>
-      <c r="L75" s="11"/>
+      <c r="K75" s="38"/>
+      <c r="L75" s="8"/>
     </row>
     <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="3"/>
+      <c r="A76" s="35"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
@@ -1844,11 +2324,11 @@
       <c r="H76" s="3"/>
       <c r="I76" s="4"/>
       <c r="J76" s="5"/>
-      <c r="K76" s="10"/>
-      <c r="L76" s="11"/>
+      <c r="K76" s="38"/>
+      <c r="L76" s="8"/>
     </row>
     <row r="77" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="3"/>
+      <c r="A77" s="35"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
@@ -1858,11 +2338,11 @@
       <c r="H77" s="3"/>
       <c r="I77" s="4"/>
       <c r="J77" s="5"/>
-      <c r="K77" s="10"/>
-      <c r="L77" s="11"/>
+      <c r="K77" s="38"/>
+      <c r="L77" s="8"/>
     </row>
     <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="3"/>
+      <c r="A78" s="35"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
@@ -1872,11 +2352,11 @@
       <c r="H78" s="3"/>
       <c r="I78" s="4"/>
       <c r="J78" s="5"/>
-      <c r="K78" s="10"/>
-      <c r="L78" s="11"/>
+      <c r="K78" s="38"/>
+      <c r="L78" s="8"/>
     </row>
     <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="3"/>
+      <c r="A79" s="35"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
@@ -1886,11 +2366,11 @@
       <c r="H79" s="3"/>
       <c r="I79" s="4"/>
       <c r="J79" s="5"/>
-      <c r="K79" s="10"/>
-      <c r="L79" s="11"/>
+      <c r="K79" s="38"/>
+      <c r="L79" s="8"/>
     </row>
     <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="3"/>
+      <c r="A80" s="35"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
@@ -1900,11 +2380,11 @@
       <c r="H80" s="3"/>
       <c r="I80" s="4"/>
       <c r="J80" s="5"/>
-      <c r="K80" s="10"/>
-      <c r="L80" s="11"/>
+      <c r="K80" s="38"/>
+      <c r="L80" s="8"/>
     </row>
     <row r="81" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="3"/>
+      <c r="A81" s="35"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
@@ -1914,11 +2394,11 @@
       <c r="H81" s="3"/>
       <c r="I81" s="4"/>
       <c r="J81" s="5"/>
-      <c r="K81" s="10"/>
-      <c r="L81" s="11"/>
+      <c r="K81" s="38"/>
+      <c r="L81" s="8"/>
     </row>
     <row r="82" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="3"/>
+      <c r="A82" s="35"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
@@ -1928,11 +2408,11 @@
       <c r="H82" s="3"/>
       <c r="I82" s="4"/>
       <c r="J82" s="5"/>
-      <c r="K82" s="10"/>
-      <c r="L82" s="11"/>
+      <c r="K82" s="38"/>
+      <c r="L82" s="8"/>
     </row>
     <row r="83" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="3"/>
+      <c r="A83" s="35"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
@@ -1942,11 +2422,11 @@
       <c r="H83" s="3"/>
       <c r="I83" s="4"/>
       <c r="J83" s="5"/>
-      <c r="K83" s="10"/>
-      <c r="L83" s="11"/>
+      <c r="K83" s="38"/>
+      <c r="L83" s="8"/>
     </row>
     <row r="84" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="3"/>
+      <c r="A84" s="35"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
@@ -1956,11 +2436,11 @@
       <c r="H84" s="3"/>
       <c r="I84" s="4"/>
       <c r="J84" s="5"/>
-      <c r="K84" s="10"/>
-      <c r="L84" s="11"/>
+      <c r="K84" s="38"/>
+      <c r="L84" s="8"/>
     </row>
     <row r="85" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="3"/>
+      <c r="A85" s="35"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
@@ -1970,11 +2450,11 @@
       <c r="H85" s="3"/>
       <c r="I85" s="4"/>
       <c r="J85" s="5"/>
-      <c r="K85" s="10"/>
-      <c r="L85" s="11"/>
+      <c r="K85" s="38"/>
+      <c r="L85" s="8"/>
     </row>
     <row r="86" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="3"/>
+      <c r="A86" s="35"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
@@ -1984,11 +2464,11 @@
       <c r="H86" s="3"/>
       <c r="I86" s="4"/>
       <c r="J86" s="5"/>
-      <c r="K86" s="10"/>
-      <c r="L86" s="11"/>
+      <c r="K86" s="38"/>
+      <c r="L86" s="8"/>
     </row>
     <row r="87" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="3"/>
+      <c r="A87" s="35"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
@@ -1998,11 +2478,11 @@
       <c r="H87" s="3"/>
       <c r="I87" s="4"/>
       <c r="J87" s="5"/>
-      <c r="K87" s="10"/>
-      <c r="L87" s="11"/>
+      <c r="K87" s="38"/>
+      <c r="L87" s="8"/>
     </row>
     <row r="88" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="3"/>
+      <c r="A88" s="35"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
@@ -2012,11 +2492,11 @@
       <c r="H88" s="3"/>
       <c r="I88" s="4"/>
       <c r="J88" s="5"/>
-      <c r="K88" s="10"/>
-      <c r="L88" s="11"/>
+      <c r="K88" s="38"/>
+      <c r="L88" s="8"/>
     </row>
     <row r="89" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="3"/>
+      <c r="A89" s="35"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
@@ -2026,11 +2506,11 @@
       <c r="H89" s="3"/>
       <c r="I89" s="4"/>
       <c r="J89" s="5"/>
-      <c r="K89" s="10"/>
-      <c r="L89" s="11"/>
+      <c r="K89" s="38"/>
+      <c r="L89" s="8"/>
     </row>
     <row r="90" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="3"/>
+      <c r="A90" s="35"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
@@ -2040,11 +2520,11 @@
       <c r="H90" s="3"/>
       <c r="I90" s="4"/>
       <c r="J90" s="5"/>
-      <c r="K90" s="10"/>
-      <c r="L90" s="11"/>
+      <c r="K90" s="38"/>
+      <c r="L90" s="8"/>
     </row>
     <row r="91" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="3"/>
+      <c r="A91" s="35"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
@@ -2054,11 +2534,11 @@
       <c r="H91" s="3"/>
       <c r="I91" s="4"/>
       <c r="J91" s="5"/>
-      <c r="K91" s="10"/>
-      <c r="L91" s="11"/>
+      <c r="K91" s="38"/>
+      <c r="L91" s="8"/>
     </row>
     <row r="92" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="3"/>
+      <c r="A92" s="35"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
@@ -2068,11 +2548,11 @@
       <c r="H92" s="3"/>
       <c r="I92" s="4"/>
       <c r="J92" s="5"/>
-      <c r="K92" s="10"/>
-      <c r="L92" s="11"/>
+      <c r="K92" s="38"/>
+      <c r="L92" s="8"/>
     </row>
     <row r="93" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="3"/>
+      <c r="A93" s="35"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
@@ -2082,11 +2562,11 @@
       <c r="H93" s="3"/>
       <c r="I93" s="4"/>
       <c r="J93" s="5"/>
-      <c r="K93" s="10"/>
-      <c r="L93" s="11"/>
+      <c r="K93" s="38"/>
+      <c r="L93" s="8"/>
     </row>
     <row r="94" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="3"/>
+      <c r="A94" s="35"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
@@ -2096,11 +2576,11 @@
       <c r="H94" s="3"/>
       <c r="I94" s="4"/>
       <c r="J94" s="5"/>
-      <c r="K94" s="10"/>
-      <c r="L94" s="11"/>
+      <c r="K94" s="38"/>
+      <c r="L94" s="8"/>
     </row>
     <row r="95" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="3"/>
+      <c r="A95" s="35"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
@@ -2110,11 +2590,11 @@
       <c r="H95" s="3"/>
       <c r="I95" s="4"/>
       <c r="J95" s="5"/>
-      <c r="K95" s="10"/>
-      <c r="L95" s="11"/>
+      <c r="K95" s="38"/>
+      <c r="L95" s="8"/>
     </row>
     <row r="96" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="3"/>
+      <c r="A96" s="35"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
@@ -2124,11 +2604,11 @@
       <c r="H96" s="3"/>
       <c r="I96" s="4"/>
       <c r="J96" s="5"/>
-      <c r="K96" s="10"/>
-      <c r="L96" s="11"/>
+      <c r="K96" s="38"/>
+      <c r="L96" s="8"/>
     </row>
     <row r="97" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="3"/>
+      <c r="A97" s="35"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
@@ -2138,11 +2618,11 @@
       <c r="H97" s="3"/>
       <c r="I97" s="4"/>
       <c r="J97" s="5"/>
-      <c r="K97" s="10"/>
-      <c r="L97" s="11"/>
+      <c r="K97" s="38"/>
+      <c r="L97" s="8"/>
     </row>
     <row r="98" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="3"/>
+      <c r="A98" s="35"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
@@ -2152,11 +2632,11 @@
       <c r="H98" s="3"/>
       <c r="I98" s="4"/>
       <c r="J98" s="5"/>
-      <c r="K98" s="10"/>
-      <c r="L98" s="11"/>
+      <c r="K98" s="38"/>
+      <c r="L98" s="8"/>
     </row>
     <row r="99" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="3"/>
+      <c r="A99" s="35"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
@@ -2166,11 +2646,11 @@
       <c r="H99" s="3"/>
       <c r="I99" s="4"/>
       <c r="J99" s="5"/>
-      <c r="K99" s="10"/>
-      <c r="L99" s="11"/>
+      <c r="K99" s="38"/>
+      <c r="L99" s="8"/>
     </row>
     <row r="100" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="3"/>
+      <c r="A100" s="35"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
@@ -2180,11 +2660,11 @@
       <c r="H100" s="3"/>
       <c r="I100" s="4"/>
       <c r="J100" s="5"/>
-      <c r="K100" s="10"/>
-      <c r="L100" s="11"/>
+      <c r="K100" s="38"/>
+      <c r="L100" s="8"/>
     </row>
     <row r="101" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="3"/>
+      <c r="A101" s="35"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
@@ -2194,11 +2674,11 @@
       <c r="H101" s="3"/>
       <c r="I101" s="4"/>
       <c r="J101" s="5"/>
-      <c r="K101" s="10"/>
-      <c r="L101" s="11"/>
+      <c r="K101" s="38"/>
+      <c r="L101" s="8"/>
     </row>
     <row r="102" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="3"/>
+      <c r="A102" s="35"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
@@ -2208,11 +2688,11 @@
       <c r="H102" s="3"/>
       <c r="I102" s="4"/>
       <c r="J102" s="5"/>
-      <c r="K102" s="10"/>
-      <c r="L102" s="11"/>
+      <c r="K102" s="38"/>
+      <c r="L102" s="8"/>
     </row>
     <row r="103" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="3"/>
+      <c r="A103" s="35"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
@@ -2222,11 +2702,11 @@
       <c r="H103" s="3"/>
       <c r="I103" s="4"/>
       <c r="J103" s="5"/>
-      <c r="K103" s="10"/>
-      <c r="L103" s="11"/>
+      <c r="K103" s="38"/>
+      <c r="L103" s="8"/>
     </row>
     <row r="104" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="3"/>
+      <c r="A104" s="35"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
@@ -2236,11 +2716,11 @@
       <c r="H104" s="3"/>
       <c r="I104" s="4"/>
       <c r="J104" s="5"/>
-      <c r="K104" s="10"/>
-      <c r="L104" s="11"/>
+      <c r="K104" s="38"/>
+      <c r="L104" s="8"/>
     </row>
     <row r="105" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="3"/>
+      <c r="A105" s="35"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
@@ -2250,11 +2730,11 @@
       <c r="H105" s="3"/>
       <c r="I105" s="4"/>
       <c r="J105" s="5"/>
-      <c r="K105" s="10"/>
-      <c r="L105" s="11"/>
+      <c r="K105" s="38"/>
+      <c r="L105" s="8"/>
     </row>
     <row r="106" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="3"/>
+      <c r="A106" s="35"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
@@ -2264,11 +2744,11 @@
       <c r="H106" s="3"/>
       <c r="I106" s="4"/>
       <c r="J106" s="5"/>
-      <c r="K106" s="10"/>
-      <c r="L106" s="11"/>
+      <c r="K106" s="38"/>
+      <c r="L106" s="8"/>
     </row>
     <row r="107" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="3"/>
+      <c r="A107" s="35"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
@@ -2278,11 +2758,11 @@
       <c r="H107" s="3"/>
       <c r="I107" s="4"/>
       <c r="J107" s="5"/>
-      <c r="K107" s="10"/>
-      <c r="L107" s="11"/>
+      <c r="K107" s="38"/>
+      <c r="L107" s="8"/>
     </row>
     <row r="108" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="3"/>
+      <c r="A108" s="35"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
@@ -2292,11 +2772,11 @@
       <c r="H108" s="3"/>
       <c r="I108" s="4"/>
       <c r="J108" s="5"/>
-      <c r="K108" s="10"/>
-      <c r="L108" s="11"/>
+      <c r="K108" s="38"/>
+      <c r="L108" s="8"/>
     </row>
     <row r="109" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="3"/>
+      <c r="A109" s="35"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
@@ -2306,11 +2786,11 @@
       <c r="H109" s="3"/>
       <c r="I109" s="4"/>
       <c r="J109" s="5"/>
-      <c r="K109" s="10"/>
-      <c r="L109" s="11"/>
+      <c r="K109" s="38"/>
+      <c r="L109" s="8"/>
     </row>
     <row r="110" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="3"/>
+      <c r="A110" s="35"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
@@ -2320,11 +2800,11 @@
       <c r="H110" s="3"/>
       <c r="I110" s="4"/>
       <c r="J110" s="5"/>
-      <c r="K110" s="10"/>
-      <c r="L110" s="11"/>
+      <c r="K110" s="38"/>
+      <c r="L110" s="8"/>
     </row>
     <row r="111" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="3"/>
+      <c r="A111" s="35"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
@@ -2334,11 +2814,11 @@
       <c r="H111" s="3"/>
       <c r="I111" s="4"/>
       <c r="J111" s="5"/>
-      <c r="K111" s="10"/>
-      <c r="L111" s="11"/>
+      <c r="K111" s="38"/>
+      <c r="L111" s="8"/>
     </row>
     <row r="112" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="3"/>
+      <c r="A112" s="35"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
@@ -2348,11 +2828,11 @@
       <c r="H112" s="3"/>
       <c r="I112" s="4"/>
       <c r="J112" s="5"/>
-      <c r="K112" s="10"/>
-      <c r="L112" s="11"/>
+      <c r="K112" s="38"/>
+      <c r="L112" s="8"/>
     </row>
     <row r="113" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="3"/>
+      <c r="A113" s="35"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
@@ -2362,11 +2842,11 @@
       <c r="H113" s="3"/>
       <c r="I113" s="4"/>
       <c r="J113" s="5"/>
-      <c r="K113" s="10"/>
-      <c r="L113" s="11"/>
+      <c r="K113" s="38"/>
+      <c r="L113" s="8"/>
     </row>
     <row r="114" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="3"/>
+      <c r="A114" s="35"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
@@ -2376,11 +2856,11 @@
       <c r="H114" s="3"/>
       <c r="I114" s="4"/>
       <c r="J114" s="5"/>
-      <c r="K114" s="10"/>
-      <c r="L114" s="11"/>
+      <c r="K114" s="38"/>
+      <c r="L114" s="8"/>
     </row>
     <row r="115" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="3"/>
+      <c r="A115" s="35"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
@@ -2390,11 +2870,11 @@
       <c r="H115" s="3"/>
       <c r="I115" s="4"/>
       <c r="J115" s="5"/>
-      <c r="K115" s="10"/>
-      <c r="L115" s="11"/>
+      <c r="K115" s="38"/>
+      <c r="L115" s="8"/>
     </row>
     <row r="116" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="3"/>
+      <c r="A116" s="35"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
@@ -2404,11 +2884,11 @@
       <c r="H116" s="3"/>
       <c r="I116" s="4"/>
       <c r="J116" s="5"/>
-      <c r="K116" s="10"/>
-      <c r="L116" s="11"/>
+      <c r="K116" s="38"/>
+      <c r="L116" s="8"/>
     </row>
     <row r="117" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="3"/>
+      <c r="A117" s="35"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
@@ -2418,11 +2898,11 @@
       <c r="H117" s="3"/>
       <c r="I117" s="4"/>
       <c r="J117" s="5"/>
-      <c r="K117" s="10"/>
-      <c r="L117" s="11"/>
+      <c r="K117" s="38"/>
+      <c r="L117" s="8"/>
     </row>
     <row r="118" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="3"/>
+      <c r="A118" s="35"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
@@ -2432,11 +2912,11 @@
       <c r="H118" s="3"/>
       <c r="I118" s="4"/>
       <c r="J118" s="5"/>
-      <c r="K118" s="10"/>
-      <c r="L118" s="11"/>
+      <c r="K118" s="38"/>
+      <c r="L118" s="8"/>
     </row>
     <row r="119" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="3"/>
+      <c r="A119" s="35"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
@@ -2446,11 +2926,11 @@
       <c r="H119" s="3"/>
       <c r="I119" s="4"/>
       <c r="J119" s="5"/>
-      <c r="K119" s="10"/>
-      <c r="L119" s="11"/>
+      <c r="K119" s="38"/>
+      <c r="L119" s="8"/>
     </row>
     <row r="120" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="3"/>
+      <c r="A120" s="35"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
@@ -2460,11 +2940,11 @@
       <c r="H120" s="3"/>
       <c r="I120" s="4"/>
       <c r="J120" s="5"/>
-      <c r="K120" s="10"/>
-      <c r="L120" s="11"/>
+      <c r="K120" s="38"/>
+      <c r="L120" s="8"/>
     </row>
     <row r="121" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="3"/>
+      <c r="A121" s="35"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
@@ -2474,11 +2954,11 @@
       <c r="H121" s="3"/>
       <c r="I121" s="4"/>
       <c r="J121" s="5"/>
-      <c r="K121" s="10"/>
-      <c r="L121" s="11"/>
+      <c r="K121" s="38"/>
+      <c r="L121" s="8"/>
     </row>
     <row r="122" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="3"/>
+      <c r="A122" s="35"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
@@ -2488,11 +2968,11 @@
       <c r="H122" s="3"/>
       <c r="I122" s="4"/>
       <c r="J122" s="5"/>
-      <c r="K122" s="10"/>
-      <c r="L122" s="11"/>
+      <c r="K122" s="38"/>
+      <c r="L122" s="8"/>
     </row>
     <row r="123" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="3"/>
+      <c r="A123" s="35"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
@@ -2502,11 +2982,11 @@
       <c r="H123" s="3"/>
       <c r="I123" s="4"/>
       <c r="J123" s="5"/>
-      <c r="K123" s="10"/>
-      <c r="L123" s="11"/>
+      <c r="K123" s="38"/>
+      <c r="L123" s="8"/>
     </row>
     <row r="124" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="3"/>
+      <c r="A124" s="35"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
@@ -2516,11 +2996,11 @@
       <c r="H124" s="3"/>
       <c r="I124" s="4"/>
       <c r="J124" s="5"/>
-      <c r="K124" s="10"/>
-      <c r="L124" s="11"/>
+      <c r="K124" s="38"/>
+      <c r="L124" s="8"/>
     </row>
     <row r="125" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="3"/>
+      <c r="A125" s="35"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
@@ -2530,11 +3010,11 @@
       <c r="H125" s="3"/>
       <c r="I125" s="4"/>
       <c r="J125" s="5"/>
-      <c r="K125" s="10"/>
-      <c r="L125" s="11"/>
+      <c r="K125" s="38"/>
+      <c r="L125" s="8"/>
     </row>
     <row r="126" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="3"/>
+      <c r="A126" s="35"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
@@ -2544,11 +3024,11 @@
       <c r="H126" s="3"/>
       <c r="I126" s="4"/>
       <c r="J126" s="5"/>
-      <c r="K126" s="10"/>
-      <c r="L126" s="11"/>
+      <c r="K126" s="38"/>
+      <c r="L126" s="8"/>
     </row>
     <row r="127" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="3"/>
+      <c r="A127" s="35"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
@@ -2558,11 +3038,11 @@
       <c r="H127" s="3"/>
       <c r="I127" s="4"/>
       <c r="J127" s="5"/>
-      <c r="K127" s="10"/>
-      <c r="L127" s="11"/>
+      <c r="K127" s="38"/>
+      <c r="L127" s="8"/>
     </row>
     <row r="128" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="3"/>
+      <c r="A128" s="35"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
@@ -2572,11 +3052,11 @@
       <c r="H128" s="3"/>
       <c r="I128" s="4"/>
       <c r="J128" s="5"/>
-      <c r="K128" s="10"/>
-      <c r="L128" s="11"/>
+      <c r="K128" s="38"/>
+      <c r="L128" s="8"/>
     </row>
     <row r="129" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="3"/>
+      <c r="A129" s="35"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
@@ -2586,11 +3066,11 @@
       <c r="H129" s="3"/>
       <c r="I129" s="4"/>
       <c r="J129" s="5"/>
-      <c r="K129" s="10"/>
-      <c r="L129" s="11"/>
+      <c r="K129" s="38"/>
+      <c r="L129" s="8"/>
     </row>
     <row r="130" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="3"/>
+      <c r="A130" s="35"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
@@ -2600,11 +3080,11 @@
       <c r="H130" s="3"/>
       <c r="I130" s="4"/>
       <c r="J130" s="5"/>
-      <c r="K130" s="10"/>
-      <c r="L130" s="11"/>
+      <c r="K130" s="38"/>
+      <c r="L130" s="8"/>
     </row>
     <row r="131" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="3"/>
+      <c r="A131" s="35"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
@@ -2614,11 +3094,11 @@
       <c r="H131" s="3"/>
       <c r="I131" s="4"/>
       <c r="J131" s="5"/>
-      <c r="K131" s="10"/>
-      <c r="L131" s="11"/>
+      <c r="K131" s="38"/>
+      <c r="L131" s="8"/>
     </row>
     <row r="132" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="3"/>
+      <c r="A132" s="35"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
@@ -2628,11 +3108,11 @@
       <c r="H132" s="3"/>
       <c r="I132" s="4"/>
       <c r="J132" s="5"/>
-      <c r="K132" s="10"/>
-      <c r="L132" s="11"/>
+      <c r="K132" s="38"/>
+      <c r="L132" s="8"/>
     </row>
     <row r="133" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="3"/>
+      <c r="A133" s="35"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
@@ -2642,11 +3122,11 @@
       <c r="H133" s="3"/>
       <c r="I133" s="4"/>
       <c r="J133" s="5"/>
-      <c r="K133" s="10"/>
-      <c r="L133" s="11"/>
+      <c r="K133" s="38"/>
+      <c r="L133" s="8"/>
     </row>
     <row r="134" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="3"/>
+      <c r="A134" s="35"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
@@ -2656,11 +3136,11 @@
       <c r="H134" s="3"/>
       <c r="I134" s="4"/>
       <c r="J134" s="5"/>
-      <c r="K134" s="10"/>
-      <c r="L134" s="11"/>
+      <c r="K134" s="38"/>
+      <c r="L134" s="8"/>
     </row>
     <row r="135" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A135" s="3"/>
+      <c r="A135" s="35"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
@@ -2670,11 +3150,11 @@
       <c r="H135" s="3"/>
       <c r="I135" s="4"/>
       <c r="J135" s="5"/>
-      <c r="K135" s="10"/>
-      <c r="L135" s="11"/>
+      <c r="K135" s="38"/>
+      <c r="L135" s="8"/>
     </row>
     <row r="136" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="3"/>
+      <c r="A136" s="35"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
@@ -2684,11 +3164,11 @@
       <c r="H136" s="3"/>
       <c r="I136" s="4"/>
       <c r="J136" s="5"/>
-      <c r="K136" s="10"/>
-      <c r="L136" s="11"/>
+      <c r="K136" s="38"/>
+      <c r="L136" s="8"/>
     </row>
     <row r="137" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A137" s="3"/>
+      <c r="A137" s="35"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
@@ -2698,11 +3178,11 @@
       <c r="H137" s="3"/>
       <c r="I137" s="4"/>
       <c r="J137" s="5"/>
-      <c r="K137" s="10"/>
-      <c r="L137" s="11"/>
+      <c r="K137" s="38"/>
+      <c r="L137" s="8"/>
     </row>
     <row r="138" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A138" s="3"/>
+      <c r="A138" s="35"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
@@ -2712,11 +3192,11 @@
       <c r="H138" s="3"/>
       <c r="I138" s="4"/>
       <c r="J138" s="5"/>
-      <c r="K138" s="10"/>
-      <c r="L138" s="11"/>
+      <c r="K138" s="38"/>
+      <c r="L138" s="8"/>
     </row>
     <row r="139" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A139" s="3"/>
+      <c r="A139" s="35"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
@@ -2726,11 +3206,11 @@
       <c r="H139" s="3"/>
       <c r="I139" s="4"/>
       <c r="J139" s="5"/>
-      <c r="K139" s="10"/>
-      <c r="L139" s="11"/>
+      <c r="K139" s="38"/>
+      <c r="L139" s="8"/>
     </row>
     <row r="140" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="3"/>
+      <c r="A140" s="35"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
@@ -2740,11 +3220,11 @@
       <c r="H140" s="3"/>
       <c r="I140" s="4"/>
       <c r="J140" s="5"/>
-      <c r="K140" s="10"/>
-      <c r="L140" s="11"/>
+      <c r="K140" s="38"/>
+      <c r="L140" s="8"/>
     </row>
     <row r="141" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="3"/>
+      <c r="A141" s="35"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
@@ -2754,11 +3234,11 @@
       <c r="H141" s="3"/>
       <c r="I141" s="4"/>
       <c r="J141" s="5"/>
-      <c r="K141" s="10"/>
-      <c r="L141" s="11"/>
+      <c r="K141" s="38"/>
+      <c r="L141" s="8"/>
     </row>
     <row r="142" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A142" s="3"/>
+      <c r="A142" s="35"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
@@ -2768,11 +3248,11 @@
       <c r="H142" s="3"/>
       <c r="I142" s="4"/>
       <c r="J142" s="5"/>
-      <c r="K142" s="10"/>
-      <c r="L142" s="11"/>
+      <c r="K142" s="38"/>
+      <c r="L142" s="8"/>
     </row>
     <row r="143" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A143" s="3"/>
+      <c r="A143" s="35"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
@@ -2782,11 +3262,11 @@
       <c r="H143" s="3"/>
       <c r="I143" s="4"/>
       <c r="J143" s="5"/>
-      <c r="K143" s="10"/>
-      <c r="L143" s="11"/>
+      <c r="K143" s="38"/>
+      <c r="L143" s="8"/>
     </row>
     <row r="144" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A144" s="3"/>
+      <c r="A144" s="35"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
@@ -2796,11 +3276,11 @@
       <c r="H144" s="3"/>
       <c r="I144" s="4"/>
       <c r="J144" s="5"/>
-      <c r="K144" s="10"/>
-      <c r="L144" s="11"/>
+      <c r="K144" s="38"/>
+      <c r="L144" s="8"/>
     </row>
     <row r="145" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A145" s="3"/>
+      <c r="A145" s="35"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
@@ -2810,11 +3290,11 @@
       <c r="H145" s="3"/>
       <c r="I145" s="4"/>
       <c r="J145" s="5"/>
-      <c r="K145" s="10"/>
-      <c r="L145" s="11"/>
+      <c r="K145" s="38"/>
+      <c r="L145" s="8"/>
     </row>
     <row r="146" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A146" s="3"/>
+      <c r="A146" s="35"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
@@ -2824,11 +3304,11 @@
       <c r="H146" s="3"/>
       <c r="I146" s="4"/>
       <c r="J146" s="5"/>
-      <c r="K146" s="10"/>
-      <c r="L146" s="11"/>
+      <c r="K146" s="38"/>
+      <c r="L146" s="8"/>
     </row>
     <row r="147" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A147" s="3"/>
+      <c r="A147" s="35"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
@@ -2838,11 +3318,11 @@
       <c r="H147" s="3"/>
       <c r="I147" s="4"/>
       <c r="J147" s="5"/>
-      <c r="K147" s="10"/>
-      <c r="L147" s="11"/>
+      <c r="K147" s="38"/>
+      <c r="L147" s="8"/>
     </row>
     <row r="148" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A148" s="3"/>
+      <c r="A148" s="35"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
@@ -2852,11 +3332,11 @@
       <c r="H148" s="3"/>
       <c r="I148" s="4"/>
       <c r="J148" s="5"/>
-      <c r="K148" s="10"/>
-      <c r="L148" s="11"/>
+      <c r="K148" s="38"/>
+      <c r="L148" s="8"/>
     </row>
     <row r="149" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A149" s="3"/>
+      <c r="A149" s="35"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
@@ -2866,11 +3346,11 @@
       <c r="H149" s="3"/>
       <c r="I149" s="4"/>
       <c r="J149" s="5"/>
-      <c r="K149" s="10"/>
-      <c r="L149" s="11"/>
+      <c r="K149" s="38"/>
+      <c r="L149" s="8"/>
     </row>
     <row r="150" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A150" s="3"/>
+      <c r="A150" s="35"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
@@ -2880,11 +3360,11 @@
       <c r="H150" s="3"/>
       <c r="I150" s="4"/>
       <c r="J150" s="5"/>
-      <c r="K150" s="10"/>
-      <c r="L150" s="11"/>
+      <c r="K150" s="38"/>
+      <c r="L150" s="8"/>
     </row>
     <row r="151" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A151" s="3"/>
+      <c r="A151" s="35"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
@@ -2894,11 +3374,11 @@
       <c r="H151" s="3"/>
       <c r="I151" s="4"/>
       <c r="J151" s="5"/>
-      <c r="K151" s="10"/>
-      <c r="L151" s="11"/>
+      <c r="K151" s="38"/>
+      <c r="L151" s="8"/>
     </row>
     <row r="152" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A152" s="3"/>
+      <c r="A152" s="35"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
@@ -2908,11 +3388,11 @@
       <c r="H152" s="3"/>
       <c r="I152" s="4"/>
       <c r="J152" s="5"/>
-      <c r="K152" s="10"/>
-      <c r="L152" s="11"/>
+      <c r="K152" s="38"/>
+      <c r="L152" s="8"/>
     </row>
     <row r="153" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A153" s="3"/>
+      <c r="A153" s="35"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
@@ -2922,11 +3402,11 @@
       <c r="H153" s="3"/>
       <c r="I153" s="4"/>
       <c r="J153" s="5"/>
-      <c r="K153" s="10"/>
-      <c r="L153" s="11"/>
+      <c r="K153" s="38"/>
+      <c r="L153" s="8"/>
     </row>
     <row r="154" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A154" s="3"/>
+      <c r="A154" s="35"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
@@ -2936,11 +3416,11 @@
       <c r="H154" s="3"/>
       <c r="I154" s="4"/>
       <c r="J154" s="5"/>
-      <c r="K154" s="10"/>
-      <c r="L154" s="11"/>
+      <c r="K154" s="38"/>
+      <c r="L154" s="8"/>
     </row>
     <row r="155" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="3"/>
+      <c r="A155" s="35"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
@@ -2950,11 +3430,11 @@
       <c r="H155" s="3"/>
       <c r="I155" s="4"/>
       <c r="J155" s="5"/>
-      <c r="K155" s="10"/>
-      <c r="L155" s="11"/>
+      <c r="K155" s="38"/>
+      <c r="L155" s="8"/>
     </row>
     <row r="156" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A156" s="3"/>
+      <c r="A156" s="35"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
@@ -2964,11 +3444,11 @@
       <c r="H156" s="3"/>
       <c r="I156" s="4"/>
       <c r="J156" s="5"/>
-      <c r="K156" s="10"/>
-      <c r="L156" s="11"/>
+      <c r="K156" s="38"/>
+      <c r="L156" s="8"/>
     </row>
     <row r="157" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="3"/>
+      <c r="A157" s="35"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
@@ -2978,11 +3458,11 @@
       <c r="H157" s="3"/>
       <c r="I157" s="4"/>
       <c r="J157" s="5"/>
-      <c r="K157" s="10"/>
-      <c r="L157" s="11"/>
+      <c r="K157" s="38"/>
+      <c r="L157" s="8"/>
     </row>
     <row r="158" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A158" s="3"/>
+      <c r="A158" s="35"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
@@ -2992,11 +3472,11 @@
       <c r="H158" s="3"/>
       <c r="I158" s="4"/>
       <c r="J158" s="5"/>
-      <c r="K158" s="10"/>
-      <c r="L158" s="11"/>
+      <c r="K158" s="38"/>
+      <c r="L158" s="8"/>
     </row>
     <row r="159" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="3"/>
+      <c r="A159" s="35"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
@@ -3006,11 +3486,11 @@
       <c r="H159" s="3"/>
       <c r="I159" s="4"/>
       <c r="J159" s="5"/>
-      <c r="K159" s="10"/>
-      <c r="L159" s="11"/>
+      <c r="K159" s="38"/>
+      <c r="L159" s="8"/>
     </row>
     <row r="160" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A160" s="3"/>
+      <c r="A160" s="35"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
@@ -3020,11 +3500,11 @@
       <c r="H160" s="3"/>
       <c r="I160" s="4"/>
       <c r="J160" s="5"/>
-      <c r="K160" s="10"/>
-      <c r="L160" s="11"/>
+      <c r="K160" s="38"/>
+      <c r="L160" s="8"/>
     </row>
     <row r="161" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A161" s="3"/>
+      <c r="A161" s="35"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
@@ -3034,11 +3514,11 @@
       <c r="H161" s="3"/>
       <c r="I161" s="4"/>
       <c r="J161" s="5"/>
-      <c r="K161" s="10"/>
-      <c r="L161" s="11"/>
+      <c r="K161" s="38"/>
+      <c r="L161" s="8"/>
     </row>
     <row r="162" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A162" s="3"/>
+      <c r="A162" s="35"/>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
       <c r="D162" s="3"/>
@@ -3048,11 +3528,11 @@
       <c r="H162" s="3"/>
       <c r="I162" s="4"/>
       <c r="J162" s="5"/>
-      <c r="K162" s="10"/>
-      <c r="L162" s="11"/>
+      <c r="K162" s="38"/>
+      <c r="L162" s="8"/>
     </row>
     <row r="163" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A163" s="3"/>
+      <c r="A163" s="35"/>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
       <c r="D163" s="3"/>
@@ -3062,11 +3542,11 @@
       <c r="H163" s="3"/>
       <c r="I163" s="4"/>
       <c r="J163" s="5"/>
-      <c r="K163" s="10"/>
-      <c r="L163" s="11"/>
+      <c r="K163" s="38"/>
+      <c r="L163" s="8"/>
     </row>
     <row r="164" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A164" s="3"/>
+      <c r="A164" s="35"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
@@ -3076,11 +3556,11 @@
       <c r="H164" s="3"/>
       <c r="I164" s="4"/>
       <c r="J164" s="5"/>
-      <c r="K164" s="10"/>
-      <c r="L164" s="11"/>
+      <c r="K164" s="38"/>
+      <c r="L164" s="8"/>
     </row>
     <row r="165" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A165" s="3"/>
+      <c r="A165" s="35"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
       <c r="D165" s="3"/>
@@ -3090,11 +3570,11 @@
       <c r="H165" s="3"/>
       <c r="I165" s="4"/>
       <c r="J165" s="5"/>
-      <c r="K165" s="10"/>
-      <c r="L165" s="11"/>
+      <c r="K165" s="38"/>
+      <c r="L165" s="8"/>
     </row>
     <row r="166" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A166" s="3"/>
+      <c r="A166" s="35"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
@@ -3104,11 +3584,11 @@
       <c r="H166" s="3"/>
       <c r="I166" s="4"/>
       <c r="J166" s="5"/>
-      <c r="K166" s="10"/>
-      <c r="L166" s="11"/>
+      <c r="K166" s="38"/>
+      <c r="L166" s="8"/>
     </row>
     <row r="167" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A167" s="3"/>
+      <c r="A167" s="35"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
       <c r="D167" s="3"/>
@@ -3118,11 +3598,11 @@
       <c r="H167" s="3"/>
       <c r="I167" s="4"/>
       <c r="J167" s="5"/>
-      <c r="K167" s="10"/>
-      <c r="L167" s="11"/>
+      <c r="K167" s="38"/>
+      <c r="L167" s="8"/>
     </row>
     <row r="168" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A168" s="3"/>
+      <c r="A168" s="35"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
       <c r="D168" s="3"/>
@@ -3132,11 +3612,11 @@
       <c r="H168" s="3"/>
       <c r="I168" s="4"/>
       <c r="J168" s="5"/>
-      <c r="K168" s="10"/>
-      <c r="L168" s="11"/>
+      <c r="K168" s="38"/>
+      <c r="L168" s="8"/>
     </row>
     <row r="169" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A169" s="3"/>
+      <c r="A169" s="35"/>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
       <c r="D169" s="3"/>
@@ -3146,11 +3626,11 @@
       <c r="H169" s="3"/>
       <c r="I169" s="4"/>
       <c r="J169" s="5"/>
-      <c r="K169" s="10"/>
-      <c r="L169" s="11"/>
+      <c r="K169" s="38"/>
+      <c r="L169" s="8"/>
     </row>
     <row r="170" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A170" s="3"/>
+      <c r="A170" s="35"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
@@ -3160,11 +3640,11 @@
       <c r="H170" s="3"/>
       <c r="I170" s="4"/>
       <c r="J170" s="5"/>
-      <c r="K170" s="10"/>
-      <c r="L170" s="11"/>
+      <c r="K170" s="38"/>
+      <c r="L170" s="8"/>
     </row>
     <row r="171" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A171" s="3"/>
+      <c r="A171" s="35"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
@@ -3174,11 +3654,11 @@
       <c r="H171" s="3"/>
       <c r="I171" s="4"/>
       <c r="J171" s="5"/>
-      <c r="K171" s="10"/>
-      <c r="L171" s="11"/>
+      <c r="K171" s="38"/>
+      <c r="L171" s="8"/>
     </row>
     <row r="172" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A172" s="3"/>
+      <c r="A172" s="35"/>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
@@ -3188,11 +3668,11 @@
       <c r="H172" s="3"/>
       <c r="I172" s="4"/>
       <c r="J172" s="5"/>
-      <c r="K172" s="10"/>
-      <c r="L172" s="11"/>
+      <c r="K172" s="38"/>
+      <c r="L172" s="8"/>
     </row>
     <row r="173" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A173" s="3"/>
+      <c r="A173" s="35"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
       <c r="D173" s="3"/>
@@ -3202,11 +3682,11 @@
       <c r="H173" s="3"/>
       <c r="I173" s="4"/>
       <c r="J173" s="5"/>
-      <c r="K173" s="10"/>
-      <c r="L173" s="11"/>
+      <c r="K173" s="38"/>
+      <c r="L173" s="8"/>
     </row>
     <row r="174" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A174" s="3"/>
+      <c r="A174" s="35"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
       <c r="D174" s="3"/>
@@ -3216,11 +3696,11 @@
       <c r="H174" s="3"/>
       <c r="I174" s="4"/>
       <c r="J174" s="5"/>
-      <c r="K174" s="10"/>
-      <c r="L174" s="11"/>
+      <c r="K174" s="38"/>
+      <c r="L174" s="8"/>
     </row>
     <row r="175" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A175" s="3"/>
+      <c r="A175" s="35"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
       <c r="D175" s="3"/>
@@ -3230,11 +3710,11 @@
       <c r="H175" s="3"/>
       <c r="I175" s="4"/>
       <c r="J175" s="5"/>
-      <c r="K175" s="10"/>
-      <c r="L175" s="11"/>
+      <c r="K175" s="38"/>
+      <c r="L175" s="8"/>
     </row>
     <row r="176" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A176" s="3"/>
+      <c r="A176" s="35"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
@@ -3244,11 +3724,11 @@
       <c r="H176" s="3"/>
       <c r="I176" s="4"/>
       <c r="J176" s="5"/>
-      <c r="K176" s="10"/>
-      <c r="L176" s="11"/>
+      <c r="K176" s="38"/>
+      <c r="L176" s="8"/>
     </row>
     <row r="177" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A177" s="3"/>
+      <c r="A177" s="35"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
       <c r="D177" s="3"/>
@@ -3258,11 +3738,11 @@
       <c r="H177" s="3"/>
       <c r="I177" s="4"/>
       <c r="J177" s="5"/>
-      <c r="K177" s="10"/>
-      <c r="L177" s="11"/>
+      <c r="K177" s="38"/>
+      <c r="L177" s="8"/>
     </row>
     <row r="178" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A178" s="3"/>
+      <c r="A178" s="35"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
       <c r="D178" s="3"/>
@@ -3272,11 +3752,11 @@
       <c r="H178" s="3"/>
       <c r="I178" s="4"/>
       <c r="J178" s="5"/>
-      <c r="K178" s="10"/>
-      <c r="L178" s="11"/>
+      <c r="K178" s="38"/>
+      <c r="L178" s="8"/>
     </row>
     <row r="179" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A179" s="3"/>
+      <c r="A179" s="35"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
       <c r="D179" s="3"/>
@@ -3286,11 +3766,11 @@
       <c r="H179" s="3"/>
       <c r="I179" s="4"/>
       <c r="J179" s="5"/>
-      <c r="K179" s="10"/>
-      <c r="L179" s="11"/>
+      <c r="K179" s="38"/>
+      <c r="L179" s="8"/>
     </row>
     <row r="180" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A180" s="3"/>
+      <c r="A180" s="35"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
@@ -3300,11 +3780,11 @@
       <c r="H180" s="3"/>
       <c r="I180" s="4"/>
       <c r="J180" s="5"/>
-      <c r="K180" s="10"/>
-      <c r="L180" s="11"/>
+      <c r="K180" s="38"/>
+      <c r="L180" s="8"/>
     </row>
     <row r="181" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A181" s="3"/>
+      <c r="A181" s="35"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
@@ -3314,11 +3794,11 @@
       <c r="H181" s="3"/>
       <c r="I181" s="4"/>
       <c r="J181" s="5"/>
-      <c r="K181" s="10"/>
-      <c r="L181" s="11"/>
+      <c r="K181" s="38"/>
+      <c r="L181" s="8"/>
     </row>
     <row r="182" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A182" s="3"/>
+      <c r="A182" s="35"/>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
       <c r="D182" s="3"/>
@@ -3328,11 +3808,11 @@
       <c r="H182" s="3"/>
       <c r="I182" s="4"/>
       <c r="J182" s="5"/>
-      <c r="K182" s="10"/>
-      <c r="L182" s="11"/>
+      <c r="K182" s="38"/>
+      <c r="L182" s="8"/>
     </row>
     <row r="183" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A183" s="3"/>
+      <c r="A183" s="35"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
@@ -3342,11 +3822,11 @@
       <c r="H183" s="3"/>
       <c r="I183" s="4"/>
       <c r="J183" s="5"/>
-      <c r="K183" s="10"/>
-      <c r="L183" s="11"/>
+      <c r="K183" s="38"/>
+      <c r="L183" s="8"/>
     </row>
     <row r="184" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A184" s="3"/>
+      <c r="A184" s="35"/>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
       <c r="D184" s="3"/>
@@ -3356,11 +3836,11 @@
       <c r="H184" s="3"/>
       <c r="I184" s="4"/>
       <c r="J184" s="5"/>
-      <c r="K184" s="10"/>
-      <c r="L184" s="11"/>
+      <c r="K184" s="38"/>
+      <c r="L184" s="8"/>
     </row>
     <row r="185" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A185" s="3"/>
+      <c r="A185" s="35"/>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
       <c r="D185" s="3"/>
@@ -3370,11 +3850,11 @@
       <c r="H185" s="3"/>
       <c r="I185" s="4"/>
       <c r="J185" s="5"/>
-      <c r="K185" s="10"/>
-      <c r="L185" s="11"/>
+      <c r="K185" s="38"/>
+      <c r="L185" s="8"/>
     </row>
     <row r="186" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A186" s="3"/>
+      <c r="A186" s="35"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
       <c r="D186" s="3"/>
@@ -3384,11 +3864,11 @@
       <c r="H186" s="3"/>
       <c r="I186" s="4"/>
       <c r="J186" s="5"/>
-      <c r="K186" s="10"/>
-      <c r="L186" s="11"/>
+      <c r="K186" s="38"/>
+      <c r="L186" s="8"/>
     </row>
     <row r="187" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A187" s="3"/>
+      <c r="A187" s="35"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
       <c r="D187" s="3"/>
@@ -3398,11 +3878,11 @@
       <c r="H187" s="3"/>
       <c r="I187" s="4"/>
       <c r="J187" s="5"/>
-      <c r="K187" s="10"/>
-      <c r="L187" s="11"/>
+      <c r="K187" s="38"/>
+      <c r="L187" s="8"/>
     </row>
     <row r="188" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A188" s="3"/>
+      <c r="A188" s="35"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
@@ -3412,11 +3892,11 @@
       <c r="H188" s="3"/>
       <c r="I188" s="4"/>
       <c r="J188" s="5"/>
-      <c r="K188" s="10"/>
-      <c r="L188" s="11"/>
+      <c r="K188" s="38"/>
+      <c r="L188" s="8"/>
     </row>
     <row r="189" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A189" s="3"/>
+      <c r="A189" s="35"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
       <c r="D189" s="3"/>
@@ -3426,11 +3906,11 @@
       <c r="H189" s="3"/>
       <c r="I189" s="4"/>
       <c r="J189" s="5"/>
-      <c r="K189" s="10"/>
-      <c r="L189" s="11"/>
+      <c r="K189" s="38"/>
+      <c r="L189" s="8"/>
     </row>
     <row r="190" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A190" s="3"/>
+      <c r="A190" s="35"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
       <c r="D190" s="3"/>
@@ -3440,11 +3920,11 @@
       <c r="H190" s="3"/>
       <c r="I190" s="4"/>
       <c r="J190" s="5"/>
-      <c r="K190" s="10"/>
-      <c r="L190" s="11"/>
+      <c r="K190" s="38"/>
+      <c r="L190" s="8"/>
     </row>
     <row r="191" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A191" s="3"/>
+      <c r="A191" s="35"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
       <c r="D191" s="3"/>
@@ -3454,11 +3934,11 @@
       <c r="H191" s="3"/>
       <c r="I191" s="4"/>
       <c r="J191" s="5"/>
-      <c r="K191" s="10"/>
-      <c r="L191" s="11"/>
+      <c r="K191" s="38"/>
+      <c r="L191" s="8"/>
     </row>
     <row r="192" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A192" s="3"/>
+      <c r="A192" s="35"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
@@ -3468,11 +3948,11 @@
       <c r="H192" s="3"/>
       <c r="I192" s="4"/>
       <c r="J192" s="5"/>
-      <c r="K192" s="10"/>
-      <c r="L192" s="11"/>
+      <c r="K192" s="38"/>
+      <c r="L192" s="8"/>
     </row>
     <row r="193" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A193" s="3"/>
+      <c r="A193" s="35"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
@@ -3482,11 +3962,11 @@
       <c r="H193" s="3"/>
       <c r="I193" s="4"/>
       <c r="J193" s="5"/>
-      <c r="K193" s="10"/>
-      <c r="L193" s="11"/>
+      <c r="K193" s="38"/>
+      <c r="L193" s="8"/>
     </row>
     <row r="194" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A194" s="3"/>
+      <c r="A194" s="35"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
@@ -3496,11 +3976,11 @@
       <c r="H194" s="3"/>
       <c r="I194" s="4"/>
       <c r="J194" s="5"/>
-      <c r="K194" s="10"/>
-      <c r="L194" s="11"/>
+      <c r="K194" s="38"/>
+      <c r="L194" s="8"/>
     </row>
     <row r="195" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A195" s="3"/>
+      <c r="A195" s="35"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
@@ -3510,11 +3990,11 @@
       <c r="H195" s="3"/>
       <c r="I195" s="4"/>
       <c r="J195" s="5"/>
-      <c r="K195" s="10"/>
-      <c r="L195" s="11"/>
+      <c r="K195" s="38"/>
+      <c r="L195" s="8"/>
     </row>
     <row r="196" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A196" s="3"/>
+      <c r="A196" s="35"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
@@ -3524,11 +4004,11 @@
       <c r="H196" s="3"/>
       <c r="I196" s="4"/>
       <c r="J196" s="5"/>
-      <c r="K196" s="10"/>
-      <c r="L196" s="11"/>
+      <c r="K196" s="38"/>
+      <c r="L196" s="8"/>
     </row>
     <row r="197" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A197" s="3"/>
+      <c r="A197" s="35"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
       <c r="D197" s="3"/>
@@ -3538,11 +4018,11 @@
       <c r="H197" s="3"/>
       <c r="I197" s="4"/>
       <c r="J197" s="5"/>
-      <c r="K197" s="10"/>
-      <c r="L197" s="11"/>
+      <c r="K197" s="38"/>
+      <c r="L197" s="8"/>
     </row>
     <row r="198" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A198" s="3"/>
+      <c r="A198" s="35"/>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
       <c r="D198" s="3"/>
@@ -3552,11 +4032,11 @@
       <c r="H198" s="3"/>
       <c r="I198" s="4"/>
       <c r="J198" s="5"/>
-      <c r="K198" s="10"/>
-      <c r="L198" s="11"/>
+      <c r="K198" s="38"/>
+      <c r="L198" s="8"/>
     </row>
     <row r="199" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A199" s="3"/>
+      <c r="A199" s="35"/>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
       <c r="D199" s="3"/>
@@ -3566,11 +4046,11 @@
       <c r="H199" s="3"/>
       <c r="I199" s="4"/>
       <c r="J199" s="5"/>
-      <c r="K199" s="10"/>
-      <c r="L199" s="11"/>
+      <c r="K199" s="38"/>
+      <c r="L199" s="8"/>
     </row>
     <row r="200" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A200" s="3"/>
+      <c r="A200" s="35"/>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
       <c r="D200" s="3"/>
@@ -3580,11 +4060,11 @@
       <c r="H200" s="3"/>
       <c r="I200" s="4"/>
       <c r="J200" s="5"/>
-      <c r="K200" s="10"/>
-      <c r="L200" s="11"/>
+      <c r="K200" s="38"/>
+      <c r="L200" s="8"/>
     </row>
     <row r="201" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A201" s="3"/>
+      <c r="A201" s="35"/>
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
       <c r="D201" s="3"/>
@@ -3594,11 +4074,11 @@
       <c r="H201" s="3"/>
       <c r="I201" s="4"/>
       <c r="J201" s="5"/>
-      <c r="K201" s="10"/>
-      <c r="L201" s="11"/>
+      <c r="K201" s="38"/>
+      <c r="L201" s="8"/>
     </row>
     <row r="202" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A202" s="3"/>
+      <c r="A202" s="35"/>
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
       <c r="D202" s="3"/>
@@ -3608,11 +4088,11 @@
       <c r="H202" s="3"/>
       <c r="I202" s="4"/>
       <c r="J202" s="5"/>
-      <c r="K202" s="10"/>
-      <c r="L202" s="11"/>
+      <c r="K202" s="38"/>
+      <c r="L202" s="8"/>
     </row>
     <row r="203" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A203" s="3"/>
+      <c r="A203" s="35"/>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
       <c r="D203" s="3"/>
@@ -3622,11 +4102,11 @@
       <c r="H203" s="3"/>
       <c r="I203" s="4"/>
       <c r="J203" s="5"/>
-      <c r="K203" s="10"/>
-      <c r="L203" s="11"/>
+      <c r="K203" s="38"/>
+      <c r="L203" s="8"/>
     </row>
     <row r="204" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A204" s="3"/>
+      <c r="A204" s="35"/>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
       <c r="D204" s="3"/>
@@ -3636,11 +4116,11 @@
       <c r="H204" s="3"/>
       <c r="I204" s="4"/>
       <c r="J204" s="5"/>
-      <c r="K204" s="10"/>
-      <c r="L204" s="11"/>
+      <c r="K204" s="38"/>
+      <c r="L204" s="8"/>
     </row>
     <row r="205" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A205" s="3"/>
+      <c r="A205" s="35"/>
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
       <c r="D205" s="3"/>
@@ -3650,22 +4130,22 @@
       <c r="H205" s="3"/>
       <c r="I205" s="4"/>
       <c r="J205" s="5"/>
-      <c r="K205" s="10"/>
-      <c r="L205" s="11"/>
+      <c r="K205" s="38"/>
+      <c r="L205" s="8"/>
     </row>
     <row r="206" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A206" s="3"/>
-      <c r="B206" s="3"/>
-      <c r="C206" s="3"/>
-      <c r="D206" s="3"/>
-      <c r="E206" s="3"/>
-      <c r="F206" s="3"/>
-      <c r="G206" s="3"/>
-      <c r="H206" s="3"/>
-      <c r="I206" s="4"/>
-      <c r="J206" s="5"/>
-      <c r="K206" s="10"/>
-      <c r="L206" s="11"/>
+      <c r="A206" s="41"/>
+      <c r="B206" s="42"/>
+      <c r="C206" s="42"/>
+      <c r="D206" s="42"/>
+      <c r="E206" s="42"/>
+      <c r="F206" s="42"/>
+      <c r="G206" s="42"/>
+      <c r="H206" s="42"/>
+      <c r="I206" s="43"/>
+      <c r="J206" s="44"/>
+      <c r="K206" s="38"/>
+      <c r="L206" s="8"/>
     </row>
     <row r="207" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="208" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -6844,21 +7324,9 @@
       <c r="J1003" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:J6" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="No"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <mergeCells count="27">
-    <mergeCell ref="L20:Q21"/>
-    <mergeCell ref="L22:L23"/>
-    <mergeCell ref="L24:L25"/>
-    <mergeCell ref="L26:L27"/>
-    <mergeCell ref="M26:Q27"/>
-    <mergeCell ref="M24:Q25"/>
-    <mergeCell ref="M22:Q23"/>
+  <mergeCells count="17">
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:J3"/>
     <mergeCell ref="L15:L16"/>
     <mergeCell ref="M11:Q12"/>
     <mergeCell ref="M13:Q14"/>
@@ -6867,20 +7335,18 @@
     <mergeCell ref="L9:Q10"/>
     <mergeCell ref="L11:L12"/>
     <mergeCell ref="L13:L14"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="L20:Q21"/>
+    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="L24:L25"/>
+    <mergeCell ref="L26:L27"/>
+    <mergeCell ref="M26:Q27"/>
+    <mergeCell ref="M24:Q25"/>
+    <mergeCell ref="M22:Q23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="0" orientation="portrait" horizontalDpi="203" verticalDpi="203"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>